--- a/github_sim3/docs/cowork-usecases.xlsx
+++ b/github_sim3/docs/cowork-usecases.xlsx
@@ -248,7 +248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -335,6 +335,15 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -729,9 +738,9 @@
           <t>1. Coworkとは</t>
         </is>
       </c>
-      <c r="B4" s="27" t="n"/>
-      <c r="C4" s="27" t="n"/>
-      <c r="D4" s="27" t="n"/>
+      <c r="B4" s="44" t="n"/>
+      <c r="C4" s="44" t="n"/>
+      <c r="D4" s="45" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="28" t="inlineStr">
@@ -748,9 +757,6 @@
           <t>「会話のやり取りというより、同僚にメッセージを残す感覚に近い」— Anthropic公式</t>
         </is>
       </c>
-      <c r="B6" s="30" t="n"/>
-      <c r="C6" s="30" t="n"/>
-      <c r="D6" s="30" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
@@ -758,9 +764,9 @@
           <t>2. 基本機能（8項目）</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n"/>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="27" t="n"/>
+      <c r="B8" s="44" t="n"/>
+      <c r="C8" s="44" t="n"/>
+      <c r="D8" s="45" t="n"/>
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
@@ -787,8 +793,8 @@
           <t>指定フォルダ内のファイル読取・編集・作成・整理・リネーム</t>
         </is>
       </c>
-      <c r="C10" s="32" t="n"/>
-      <c r="D10" s="32" t="n"/>
+      <c r="C10" s="44" t="n"/>
+      <c r="D10" s="45" t="n"/>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="31" t="inlineStr">
@@ -801,8 +807,8 @@
           <t>レポート草稿、メモからの文書生成、プレゼン資料作成（Excel/Word/PowerPoint）</t>
         </is>
       </c>
-      <c r="C11" s="32" t="n"/>
-      <c r="D11" s="32" t="n"/>
+      <c r="C11" s="44" t="n"/>
+      <c r="D11" s="45" t="n"/>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="31" t="inlineStr">
@@ -815,8 +821,8 @@
           <t>レシート・名刺のスクリーンショットからスプレッドシート作成</t>
         </is>
       </c>
-      <c r="C12" s="32" t="n"/>
-      <c r="D12" s="32" t="n"/>
+      <c r="C12" s="44" t="n"/>
+      <c r="D12" s="45" t="n"/>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="31" t="inlineStr">
@@ -829,8 +835,8 @@
           <t>複数ソースからの情報収集・統合・要約</t>
         </is>
       </c>
-      <c r="C13" s="32" t="n"/>
-      <c r="D13" s="32" t="n"/>
+      <c r="C13" s="44" t="n"/>
+      <c r="D13" s="45" t="n"/>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="31" t="inlineStr">
@@ -843,8 +849,8 @@
           <t>Chrome拡張「Claude in Chrome」と連携しWeb操作も可能</t>
         </is>
       </c>
-      <c r="C14" s="32" t="n"/>
-      <c r="D14" s="32" t="n"/>
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="45" t="n"/>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="31" t="inlineStr">
@@ -857,8 +863,8 @@
           <t>タスクを受けると自動で計画→段階的に実行→進捗報告</t>
         </is>
       </c>
-      <c r="C15" s="32" t="n"/>
-      <c r="D15" s="32" t="n"/>
+      <c r="C15" s="44" t="n"/>
+      <c r="D15" s="45" t="n"/>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="31" t="inlineStr">
@@ -871,8 +877,8 @@
           <t>複数のサブタスクを並列で実行可能</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="32" t="n"/>
+      <c r="C16" s="44" t="n"/>
+      <c r="D16" s="45" t="n"/>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="31" t="inlineStr">
@@ -885,8 +891,8 @@
           <t>MCP経由でCRM、プロジェクト管理ツール等と接続</t>
         </is>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="32" t="n"/>
+      <c r="C17" s="44" t="n"/>
+      <c r="D17" s="45" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
@@ -894,9 +900,9 @@
           <t>3. 利用条件・料金プラン</t>
         </is>
       </c>
-      <c r="B19" s="27" t="n"/>
-      <c r="C19" s="27" t="n"/>
-      <c r="D19" s="27" t="n"/>
+      <c r="B19" s="44" t="n"/>
+      <c r="C19" s="44" t="n"/>
+      <c r="D19" s="45" t="n"/>
     </row>
     <row r="20" ht="25" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
@@ -932,7 +938,7 @@
           <t>2026/1/16から利用可能。利用制限に早く到達する可能性あり</t>
         </is>
       </c>
-      <c r="D21" s="32" t="n"/>
+      <c r="D21" s="45" t="n"/>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
@@ -950,7 +956,7 @@
           <t>5時間あたり約225メッセージ以上</t>
         </is>
       </c>
-      <c r="D22" s="32" t="n"/>
+      <c r="D22" s="45" t="n"/>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
@@ -968,7 +974,7 @@
           <t>5時間あたり約900メッセージ以上</t>
         </is>
       </c>
-      <c r="D23" s="32" t="n"/>
+      <c r="D23" s="45" t="n"/>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
@@ -986,7 +992,7 @@
           <t>利用可能</t>
         </is>
       </c>
-      <c r="D24" s="32" t="n"/>
+      <c r="D24" s="45" t="n"/>
     </row>
     <row r="26" ht="25" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
@@ -994,9 +1000,9 @@
           <t>注意事項</t>
         </is>
       </c>
-      <c r="B26" s="17" t="n"/>
-      <c r="C26" s="17" t="n"/>
-      <c r="D26" s="17" t="n"/>
+      <c r="B26" s="44" t="n"/>
+      <c r="C26" s="44" t="n"/>
+      <c r="D26" s="45" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
@@ -1032,9 +1038,9 @@
           <t>4. Skills &amp; Commands の仕組み</t>
         </is>
       </c>
-      <c r="B32" s="27" t="n"/>
-      <c r="C32" s="27" t="n"/>
-      <c r="D32" s="27" t="n"/>
+      <c r="B32" s="44" t="n"/>
+      <c r="C32" s="44" t="n"/>
+      <c r="D32" s="45" t="n"/>
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="A33" s="16" t="inlineStr">
@@ -1042,9 +1048,9 @@
           <t>Skills（スキル）— Claudeが自動で使う知識</t>
         </is>
       </c>
-      <c r="B33" s="17" t="n"/>
-      <c r="C33" s="17" t="n"/>
-      <c r="D33" s="17" t="n"/>
+      <c r="B33" s="44" t="n"/>
+      <c r="C33" s="44" t="n"/>
+      <c r="D33" s="45" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -1080,9 +1086,9 @@
           <t>Commands（コマンド）— ユーザーが手動で起動するアクション</t>
         </is>
       </c>
-      <c r="B39" s="17" t="n"/>
-      <c r="C39" s="17" t="n"/>
-      <c r="D39" s="17" t="n"/>
+      <c r="B39" s="44" t="n"/>
+      <c r="C39" s="44" t="n"/>
+      <c r="D39" s="45" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
@@ -1139,7 +1145,7 @@
           <t>ユーザーが / で明示的に実行</t>
         </is>
       </c>
-      <c r="D45" s="32" t="n"/>
+      <c r="D45" s="45" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -1157,7 +1163,7 @@
           <t>特定タスクを即座に開始</t>
         </is>
       </c>
-      <c r="D46" s="32" t="n"/>
+      <c r="D46" s="45" t="n"/>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
@@ -1165,9 +1171,9 @@
           <t>5. 公式プラグイン一覧（11種）</t>
         </is>
       </c>
-      <c r="B48" s="27" t="n"/>
-      <c r="C48" s="27" t="n"/>
-      <c r="D48" s="27" t="n"/>
+      <c r="B48" s="44" t="n"/>
+      <c r="C48" s="44" t="n"/>
+      <c r="D48" s="45" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="34" t="inlineStr">
@@ -1175,9 +1181,6 @@
           <t>すべてオープンソースで GitHub anthropics/knowledge-work-plugins で公開。コーディング不要。</t>
         </is>
       </c>
-      <c r="B49" s="35" t="n"/>
-      <c r="C49" s="35" t="n"/>
-      <c r="D49" s="35" t="n"/>
     </row>
     <row r="51" ht="25" customHeight="1">
       <c r="A51" s="15" t="inlineStr">
@@ -1449,9 +1452,9 @@
           <t>プラグインのディレクトリ構成</t>
         </is>
       </c>
-      <c r="B64" s="17" t="n"/>
-      <c r="C64" s="17" t="n"/>
-      <c r="D64" s="17" t="n"/>
+      <c r="B64" s="44" t="n"/>
+      <c r="C64" s="44" t="n"/>
+      <c r="D64" s="45" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="37" t="inlineStr">
@@ -1459,9 +1462,6 @@
           <t>plugin-name/</t>
         </is>
       </c>
-      <c r="B65" s="38" t="n"/>
-      <c r="C65" s="38" t="n"/>
-      <c r="D65" s="38" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="37" t="inlineStr">
@@ -1469,9 +1469,6 @@
           <t>├── .claude-plugin/</t>
         </is>
       </c>
-      <c r="B66" s="38" t="n"/>
-      <c r="C66" s="38" t="n"/>
-      <c r="D66" s="38" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="37" t="inlineStr">
@@ -1479,9 +1476,6 @@
           <t>│   └── plugin.json          # メタデータ（必須）</t>
         </is>
       </c>
-      <c r="B67" s="38" t="n"/>
-      <c r="C67" s="38" t="n"/>
-      <c r="D67" s="38" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="37" t="inlineStr">
@@ -1489,9 +1483,6 @@
           <t>├── .mcp.json               # 外部ツール接続設定</t>
         </is>
       </c>
-      <c r="B68" s="38" t="n"/>
-      <c r="C68" s="38" t="n"/>
-      <c r="D68" s="38" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="37" t="inlineStr">
@@ -1499,9 +1490,6 @@
           <t>├── commands/               # スラッシュコマンド定義</t>
         </is>
       </c>
-      <c r="B69" s="38" t="n"/>
-      <c r="C69" s="38" t="n"/>
-      <c r="D69" s="38" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="37" t="inlineStr">
@@ -1509,9 +1497,6 @@
           <t>├── agents/                 # サブエージェント定義</t>
         </is>
       </c>
-      <c r="B70" s="38" t="n"/>
-      <c r="C70" s="38" t="n"/>
-      <c r="D70" s="38" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="37" t="inlineStr">
@@ -1519,9 +1504,6 @@
           <t>├── skills/                 # スキル定義</t>
         </is>
       </c>
-      <c r="B71" s="38" t="n"/>
-      <c r="C71" s="38" t="n"/>
-      <c r="D71" s="38" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="37" t="inlineStr">
@@ -1529,9 +1511,6 @@
           <t>└── README.md</t>
         </is>
       </c>
-      <c r="B72" s="38" t="n"/>
-      <c r="C72" s="38" t="n"/>
-      <c r="D72" s="38" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="39" t="inlineStr">
@@ -1546,9 +1525,9 @@
           <t>カスタムプラグインの作り方</t>
         </is>
       </c>
-      <c r="B76" s="17" t="n"/>
-      <c r="C76" s="17" t="n"/>
-      <c r="D76" s="17" t="n"/>
+      <c r="B76" s="44" t="n"/>
+      <c r="C76" s="44" t="n"/>
+      <c r="D76" s="45" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
@@ -1577,9 +1556,9 @@
           <t>6. 活用事例ハイライト（note/zenn記事から）</t>
         </is>
       </c>
-      <c r="B81" s="27" t="n"/>
-      <c r="C81" s="27" t="n"/>
-      <c r="D81" s="27" t="n"/>
+      <c r="B81" s="44" t="n"/>
+      <c r="C81" s="44" t="n"/>
+      <c r="D81" s="45" t="n"/>
     </row>
     <row r="82" ht="25" customHeight="1">
       <c r="A82" s="15" t="inlineStr">
@@ -1615,7 +1594,7 @@
           <t>babushkai(zenn)</t>
         </is>
       </c>
-      <c r="D83" s="32" t="n"/>
+      <c r="D83" s="45" t="n"/>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
@@ -1633,7 +1612,7 @@
           <t>ぬるぽん(note)</t>
         </is>
       </c>
-      <c r="D84" s="32" t="n"/>
+      <c r="D84" s="45" t="n"/>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="5" t="inlineStr">
@@ -1651,7 +1630,7 @@
           <t>lnest_knowledge(zenn)</t>
         </is>
       </c>
-      <c r="D85" s="32" t="n"/>
+      <c r="D85" s="45" t="n"/>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
@@ -1669,7 +1648,7 @@
           <t>ぬるぽん(note)</t>
         </is>
       </c>
-      <c r="D86" s="32" t="n"/>
+      <c r="D86" s="45" t="n"/>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="5" t="inlineStr">
@@ -1687,7 +1666,7 @@
           <t>HIBARI(zenn)</t>
         </is>
       </c>
-      <c r="D87" s="32" t="n"/>
+      <c r="D87" s="45" t="n"/>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
@@ -1705,7 +1684,7 @@
           <t>HIBARI(zenn)</t>
         </is>
       </c>
-      <c r="D88" s="32" t="n"/>
+      <c r="D88" s="45" t="n"/>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="5" t="inlineStr">
@@ -1723,7 +1702,7 @@
           <t>ぬるぽん(note)</t>
         </is>
       </c>
-      <c r="D89" s="32" t="n"/>
+      <c r="D89" s="45" t="n"/>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="5" t="inlineStr">
@@ -1741,7 +1720,7 @@
           <t>HIBARI(zenn)</t>
         </is>
       </c>
-      <c r="D90" s="32" t="n"/>
+      <c r="D90" s="45" t="n"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="26" t="inlineStr">
@@ -1749,9 +1728,9 @@
           <t>7. 訴求ポイント（町民会館向け）</t>
         </is>
       </c>
-      <c r="B92" s="27" t="n"/>
-      <c r="C92" s="27" t="n"/>
-      <c r="D92" s="27" t="n"/>
+      <c r="B92" s="44" t="n"/>
+      <c r="C92" s="44" t="n"/>
+      <c r="D92" s="45" t="n"/>
     </row>
     <row r="93" ht="28" customHeight="1">
       <c r="A93" s="41" t="inlineStr">
@@ -1764,8 +1743,8 @@
           <t>日本語で指示するだけ</t>
         </is>
       </c>
-      <c r="C93" s="43" t="n"/>
-      <c r="D93" s="43" t="n"/>
+      <c r="C93" s="44" t="n"/>
+      <c r="D93" s="45" t="n"/>
     </row>
     <row r="94" ht="28" customHeight="1">
       <c r="A94" s="41" t="inlineStr">
@@ -1778,8 +1757,8 @@
           <t>事務員1時間分の人件費以下</t>
         </is>
       </c>
-      <c r="C94" s="43" t="n"/>
-      <c r="D94" s="43" t="n"/>
+      <c r="C94" s="44" t="n"/>
+      <c r="D94" s="45" t="n"/>
     </row>
     <row r="95" ht="28" customHeight="1">
       <c r="A95" s="41" t="inlineStr">
@@ -1792,8 +1771,8 @@
           <t>Coworkが作業中に窓口対応に集中できる</t>
         </is>
       </c>
-      <c r="C95" s="43" t="n"/>
-      <c r="D95" s="43" t="n"/>
+      <c r="C95" s="44" t="n"/>
+      <c r="D95" s="45" t="n"/>
     </row>
     <row r="96" ht="28" customHeight="1">
       <c r="A96" s="41" t="inlineStr">
@@ -1806,8 +1785,8 @@
           <t>毎朝30分の指示で2〜3時間分の作業を代行</t>
         </is>
       </c>
-      <c r="C96" s="43" t="n"/>
-      <c r="D96" s="43" t="n"/>
+      <c r="C96" s="44" t="n"/>
+      <c r="D96" s="45" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="66">
@@ -5611,17 +5590,1125 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>4.クリエイティブ系（Markdownファイル docs/cowork-usecases.md を参照）</t>
+    <row r="1" ht="35" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>4. クリエイティブ・コンテンツ制作系（50件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>活用用途</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>信頼度</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>ブログ・記事・長文ライティング</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+    </row>
+    <row r="5" ht="35" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>ブログ記事の下書き作成</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>メモや調査資料から構成付きブログ記事ドラフトをMarkdownで自動生成</t>
+        </is>
+      </c>
+      <c r="D5" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="35" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>SEO最適化記事の執筆</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>キーワードリサーチ結果を元に見出し構成・本文・メタディスクリプションを一括生成</t>
+        </is>
+      </c>
+      <c r="D6" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="35" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>技術記事・チュートリアルの作成</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>コードファイルやドキュメントからステップバイステップ技術解説記事を生成</t>
+        </is>
+      </c>
+      <c r="D7" s="47" t="inlineStr">
+        <is>
+          <t>論理的導出</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="35" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>ケーススタディの作成</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>顧客データ・プロジェクト資料から課題→解決策→成果の構成で自動生成</t>
+        </is>
+      </c>
+      <c r="D8" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="35" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>ホワイトペーパーの下書き</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>複数の調査レポートやデータを統合し専門的なホワイトペーパーの草稿を作成</t>
+        </is>
+      </c>
+      <c r="D9" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="35" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>書籍・電子書籍の執筆支援</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>章立て・アウトラインから各章の草稿まで長文コンテンツを生成</t>
+        </is>
+      </c>
+      <c r="D10" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="35" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>リサーチレポート・文献レビューの作成</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>20-50本の論文PDFを分析しテーマ別に整理された文献レビューを引用付きで生成</t>
+        </is>
+      </c>
+      <c r="D11" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="35" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>コラム・オピニオン記事の作成</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>テーマとトーンを指定し独自の視点を持った意見記事の下書きを生成</t>
+        </is>
+      </c>
+      <c r="D12" s="47" t="inlineStr">
+        <is>
+          <t>論理的導出</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="25" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>マーケティングコンテンツ</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+    </row>
+    <row r="14" ht="35" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>SNS投稿文（Twitter/X）の一括作成</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>ブログ記事1本からTwitterスレッド形式の複数投稿を自動生成</t>
+        </is>
+      </c>
+      <c r="D14" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="35" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>LinkedIn投稿の作成</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>ブログやレポートの内容をLinkedIn向けプロフェッショナルなトーンにリライト</t>
+        </is>
+      </c>
+      <c r="D15" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="35" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>Instagram投稿キャプションの作成</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>イベント情報からInstagramストーリーズ・投稿用キャプションを生成</t>
+        </is>
+      </c>
+      <c r="D16" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="35" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>メールニュースレターの作成</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>複数のブログ記事・ニュースソースを要約し配信用ニュースレター本文を構成</t>
+        </is>
+      </c>
+      <c r="D17" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="35" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>メールナーチャリングシーケンスの作成</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>5-10通のドリップメールシリーズを一括生成しCTA配置まで設計</t>
+        </is>
+      </c>
+      <c r="D18" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="35" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>ランディングページのコピー作成</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>ペルソナ・USP・CTAを指定しコンバージョン最適化されたLP文面を生成</t>
+        </is>
+      </c>
+      <c r="D19" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="35" customHeight="1">
+      <c r="A20" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>広告コピーのバリエーション作成</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>1つのクリエイティブブリーフからGoogle Ads/Meta Ads向け広告コピーを数十パターン生成</t>
+        </is>
+      </c>
+      <c r="D20" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="35" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>プレスリリースの作成</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>製品情報やイベント概要からメディア向けプレスリリースのドラフトを生成</t>
+        </is>
+      </c>
+      <c r="D21" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="35" customHeight="1">
+      <c r="A22" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>コンテンツカレンダーの作成</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>SEOキーワードリスト・マーケティング目標から月間/四半期の投稿計画をスプレッドシートで生成</t>
+        </is>
+      </c>
+      <c r="D22" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="35" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>キャンペーン企画書の作成</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>目標・チャネル戦略・コンテンツカレンダー・KPIを含むキャンペーン計画書を自動生成</t>
+        </is>
+      </c>
+      <c r="D23" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="35" customHeight="1">
+      <c r="A24" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>競合分析ブリーフの作成</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>競合情報を収集・整理しポジショニングブリーフとしてまとめる</t>
+        </is>
+      </c>
+      <c r="D24" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="35" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>商品説明文（EC向け）の作成</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>商品スペックシートからECサイト掲載用の商品説明文を複数パターン生成</t>
+        </is>
+      </c>
+      <c r="D25" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="25" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>プレゼンテーション・ビジュアル資料</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+    </row>
+    <row r="27" ht="35" customHeight="1">
+      <c r="A27" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>PowerPointプレゼン資料の作成</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>メモや会議ノートからブランドガイドライン準拠のPowerPointを直接生成</t>
+        </is>
+      </c>
+      <c r="D27" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="35" customHeight="1">
+      <c r="A28" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>Google Slidesデッキの作成</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>アウトラインからGoogle Slides互換のスライドデッキを作成</t>
+        </is>
+      </c>
+      <c r="D28" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="35" customHeight="1">
+      <c r="A29" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>営業提案書（プロポーザル）の作成</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>顧客課題・提案ソリューション・価格情報を含む提案書をフォーマット付きで生成</t>
+        </is>
+      </c>
+      <c r="D29" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="35" customHeight="1">
+      <c r="A30" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>データビジュアライゼーション付きレポート</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>CSVデータからグラフ・チャート付き分析レポートを生成</t>
+        </is>
+      </c>
+      <c r="D30" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="35" customHeight="1">
+      <c r="A31" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>インフォグラフィックの設計・SVG生成</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>データや概念をSVG形式のインフォグラフィックとして視覚化</t>
+        </is>
+      </c>
+      <c r="D31" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="35" customHeight="1">
+      <c r="A32" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>月次パフォーマンスレポートの作成</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>複数CSVからデータ抽出しExcelスプレッドシートとナラティブサマリーを含むレポートを生成</t>
+        </is>
+      </c>
+      <c r="D32" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="35" customHeight="1">
+      <c r="A33" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>会議資料・アジェンダの作成</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>議題リストから配布用の会議資料ドキュメントを生成</t>
+        </is>
+      </c>
+      <c r="D33" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="35" customHeight="1">
+      <c r="A34" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>チラシ・フライヤー文面の作成</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>イベント情報・ターゲット層を指定しキャッチコピーと本文を生成</t>
+        </is>
+      </c>
+      <c r="D34" s="47" t="inlineStr">
+        <is>
+          <t>論理的導出</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="25" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>動画・音声コンテンツ</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+    </row>
+    <row r="36" ht="35" customHeight="1">
+      <c r="A36" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>YouTube動画台本の作成</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>トピック・ターゲット視聴者を指定しフック→本編→CTAの構成で動画スクリプトを生成</t>
+        </is>
+      </c>
+      <c r="D36" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="35" customHeight="1">
+      <c r="A37" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>動画クリッピング・ショート動画化</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>長尺動画をffmpegで自動カットしSNS向け短尺クリップを生成</t>
+        </is>
+      </c>
+      <c r="D37" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="35" customHeight="1">
+      <c r="A38" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>YouTubeサムネイル設計指示書の作成</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>トップパフォーマンス動画を分析しサムネイルの構図・テキスト・配色の指示書を生成</t>
+        </is>
+      </c>
+      <c r="D38" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="35" customHeight="1">
+      <c r="A39" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>ポッドキャスト番組のショーノート作成</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>トランスクリプトから要約・タイムスタンプ・キーポイントを含むショーノートを生成</t>
+        </is>
+      </c>
+      <c r="D39" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="35" customHeight="1">
+      <c r="A40" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>ウェビナー/セミナーの台本作成</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>スライド資料と話すべきポイントからプレゼンター用台本・スピーカーノートを生成</t>
+        </is>
+      </c>
+      <c r="D40" s="47" t="inlineStr">
+        <is>
+          <t>論理的導出</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="35" customHeight="1">
+      <c r="A41" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>動画説明文・メタデータの作成</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>タイトル・説明文・タグ・ハッシュタグをプラットフォーム別に最適化して生成</t>
+        </is>
+      </c>
+      <c r="D41" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="35" customHeight="1">
+      <c r="A42" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>Explainer動画のスクリプト＋映像自動生成</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>Remotion等と連携し解説動画をスクリプトから自動生成</t>
+        </is>
+      </c>
+      <c r="D42" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="25" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>ビジネスドキュメント</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+    </row>
+    <row r="44" ht="35" customHeight="1">
+      <c r="A44" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>議事録の要約・レポート変換</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>文字起こしから決定事項・アクションアイテム・次回課題を整理した議事録を生成</t>
+        </is>
+      </c>
+      <c r="D44" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="35" customHeight="1">
+      <c r="A45" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>見積書・請求書の作成</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>テンプレートと取引データからフォーマット済みの見積書・請求書を自動生成</t>
+        </is>
+      </c>
+      <c r="D45" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="35" customHeight="1">
+      <c r="A46" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B46" s="19" t="inlineStr">
+        <is>
+          <t>契約書ドラフトの作成・レビュー</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>NDA・業務委託契約書等のドラフト作成およびリスク条項のフラグ付きレビュー</t>
+        </is>
+      </c>
+      <c r="D46" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="35" customHeight="1">
+      <c r="A47" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>社内報・社内ニュースレターの作成</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t>部署別活動報告や人事異動情報を集約し社内ニュースレターを編集</t>
+        </is>
+      </c>
+      <c r="D47" s="47" t="inlineStr">
+        <is>
+          <t>論理的導出</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="35" customHeight="1">
+      <c r="A48" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>新入社員オンボーディング資料の作成</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t>社内規定・業務マニュアルを統合しオンボーディングガイドを生成</t>
+        </is>
+      </c>
+      <c r="D48" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="35" customHeight="1">
+      <c r="A49" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>業務マニュアル・SOPの作成</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>既存の手順メモやFAQを読み込み標準作業手順書としてフォーマット</t>
+        </is>
+      </c>
+      <c r="D49" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="35" customHeight="1">
+      <c r="A50" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B50" s="19" t="inlineStr">
+        <is>
+          <t>カスタマーサポート回答テンプレートの作成</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="inlineStr">
+        <is>
+          <t>FAQ・過去問い合わせ履歴から定型回答テンプレート集を自動生成</t>
+        </is>
+      </c>
+      <c r="D50" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="35" customHeight="1">
+      <c r="A51" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B51" s="19" t="inlineStr">
+        <is>
+          <t>企画書・事業計画書の骨子作成</t>
+        </is>
+      </c>
+      <c r="C51" s="20" t="inlineStr">
+        <is>
+          <t>散在するメモ・議事録・市場データから企画書や事業計画書の骨子をまとめる</t>
+        </is>
+      </c>
+      <c r="D51" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="25" customHeight="1">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>翻訳・校正・リライト</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="n"/>
+      <c r="C52" s="17" t="n"/>
+      <c r="D52" s="17" t="n"/>
+    </row>
+    <row r="53" ht="35" customHeight="1">
+      <c r="A53" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t>多言語翻訳</t>
+        </is>
+      </c>
+      <c r="C53" s="20" t="inlineStr">
+        <is>
+          <t>ドキュメントフォルダ内のファイルを一括で他言語に翻訳（200以上の言語対応）</t>
+        </is>
+      </c>
+      <c r="D53" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="35" customHeight="1">
+      <c r="A54" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B54" s="19" t="inlineStr">
+        <is>
+          <t>校正・プルーフリーディング</t>
+        </is>
+      </c>
+      <c r="C54" s="20" t="inlineStr">
+        <is>
+          <t>文書の誤字脱字・文法エラー・表記揺れを一括チェックし修正提案を生成</t>
+        </is>
+      </c>
+      <c r="D54" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="35" customHeight="1">
+      <c r="A55" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B55" s="19" t="inlineStr">
+        <is>
+          <t>ブランドボイスレビュー・トーン調整</t>
+        </is>
+      </c>
+      <c r="C55" s="20" t="inlineStr">
+        <is>
+          <t>既存コンテンツをブランドガイドラインに照らしトーンの一貫性を確保するリライト</t>
+        </is>
+      </c>
+      <c r="D55" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="35" customHeight="1">
+      <c r="A56" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B56" s="19" t="inlineStr">
+        <is>
+          <t>コンテンツのリパーパス（再利用変換）</t>
+        </is>
+      </c>
+      <c r="C56" s="20" t="inlineStr">
+        <is>
+          <t>ブログ記事1本をLinkedIn投稿3本・Twitterスレッド・ニュースレターなどに一括変換</t>
+        </is>
+      </c>
+      <c r="D56" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="35" customHeight="1">
+      <c r="A57" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B57" s="19" t="inlineStr">
+        <is>
+          <t>ローカライゼーション</t>
+        </is>
+      </c>
+      <c r="C57" s="20" t="inlineStr">
+        <is>
+          <t>対象地域の文化的文脈に合わせたコンテンツのローカライズ</t>
+        </is>
+      </c>
+      <c r="D57" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="25" customHeight="1">
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>教育・学習コンテンツ</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="n"/>
+      <c r="C58" s="17" t="n"/>
+      <c r="D58" s="17" t="n"/>
+    </row>
+    <row r="59" ht="35" customHeight="1">
+      <c r="A59" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B59" s="19" t="inlineStr">
+        <is>
+          <t>教材・研修資料の作成</t>
+        </is>
+      </c>
+      <c r="C59" s="20" t="inlineStr">
+        <is>
+          <t>カリキュラム情報から授業計画・研修スライド・配布資料を一括生成</t>
+        </is>
+      </c>
+      <c r="D59" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="35" customHeight="1">
+      <c r="A60" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B60" s="19" t="inlineStr">
+        <is>
+          <t>クイズ・テスト問題の作成</t>
+        </is>
+      </c>
+      <c r="C60" s="20" t="inlineStr">
+        <is>
+          <t>教材テキストから選択式・記述式のテスト問題と模範解答を自動生成</t>
+        </is>
+      </c>
+      <c r="D60" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A13:D13"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5632,17 +6719,1180 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>5.データ分析系（Markdownファイル docs/cowork-usecases.md を参照）</t>
+    <row r="1" ht="35" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>5. データ分析・リサーチ系（50件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>活用用途</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>信頼度</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>データ分析基盤</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+    </row>
+    <row r="5" ht="35" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>SQLクエリ作成・最適化</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>Snowflake/BigQuery/Databricksに接続し自然言語からSQL生成。方言最適化も自動</t>
+        </is>
+      </c>
+      <c r="D5" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="35" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>インタラクティブダッシュボード構築</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>データセットからKPIチャート・グラフ含むダッシュボードを自動生成</t>
+        </is>
+      </c>
+      <c r="D6" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="35" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>データ可視化・グラフ自動生成</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>CSVやExcelから棒グラフ・折れ線・散布図・ウォーターフォールチャートを自動作成</t>
+        </is>
+      </c>
+      <c r="D7" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="35" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>統計分析（外れ値検出・クロス集計・時系列）</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>データに対して外れ値検出・クロス集計・時系列トレンド分析を数十秒で完了</t>
+        </is>
+      </c>
+      <c r="D8" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="35" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>データクレンジング・前処理</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>CSV重複削除・カラム正規化・欠損値処理・日付ソートなどの前処理を自動実行</t>
+        </is>
+      </c>
+      <c r="D9" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="35" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>データウェアハウス探索</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>テーブル構造を調査しどのJOINが必要かを自動判断してクエリ構築</t>
+        </is>
+      </c>
+      <c r="D10" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="35" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>分析結果の検証・バリデーション</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>ステークホルダー共有前にデータの整合性や計算ロジックを自動検証</t>
+        </is>
+      </c>
+      <c r="D11" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="25" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>ビジネスリサーチ・市場分析</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+    </row>
+    <row r="13" ht="35" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>市場規模推定（TAM/SAM/SOM）</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>リサーチからPowerPoint/Excelワークブック生成までエンドツーエンドで実行</t>
+        </is>
+      </c>
+      <c r="D13" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="35" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>競合分析レポート作成</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>上位5社の競合プロファイル（製品・資金調達・売上・ポジショニング）を自動調査</t>
+        </is>
+      </c>
+      <c r="D14" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="35" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>価格調査・比較分析</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>Chrome拡張で複数競合サイトを訪問し価格データをスプレッドシートにまとめて比較表作成</t>
+        </is>
+      </c>
+      <c r="D15" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="35" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>業界トレンド分析</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>Web検索・記事・論文・メモなど複数情報源から情報統合しトレンドレポートを生成</t>
+        </is>
+      </c>
+      <c r="D16" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="35" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>SWOT分析の自動作成</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>収集した市場データ・競合情報をもとに強み・弱み・機会・脅威を構造化</t>
+        </is>
+      </c>
+      <c r="D17" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="35" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>ビジネスケース・PRD作成</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>市場調査結果をもとに製品要件定義書やビジネスケースドキュメントを自動生成</t>
+        </is>
+      </c>
+      <c r="D18" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="25" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>財務・会計データ分析</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+    </row>
+    <row r="20" ht="35" customHeight="1">
+      <c r="A20" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>財務諸表分析・生成</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>月次決算データから損益計算書を自動生成し期間比較・差異分析まで実行</t>
+        </is>
+      </c>
+      <c r="D20" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="35" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>予算差異分析</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>GL残高とサブ元帳・銀行残高の照合・差異項目の特定を自動化</t>
+        </is>
+      </c>
+      <c r="D21" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="35" customHeight="1">
+      <c r="A22" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>売上予測・フォーキャスティング</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>CSVやパイプラインデータからベスト/標準/ワーストの3シナリオ予測を生成</t>
+        </is>
+      </c>
+      <c r="D22" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="35" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>経費精算・領収書OCR処理</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>領収書フォルダから日付・取引先・金額・VAT・経費カテゴリをExcel/CSVに自動抽出</t>
+        </is>
+      </c>
+      <c r="D23" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="35" customHeight="1">
+      <c r="A24" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>投資分析・ポートフォリオ評価</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>FactSet/Morningstarデータを要約しグラフ付きピッチデッキや投資メモを自動生成</t>
+        </is>
+      </c>
+      <c r="D24" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="35" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>SOXコンプライアンス監査用ワークペーパー作成</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>内部統制テスト用文書を自動生成しコンプライアンスチェック工程を効率化</t>
+        </is>
+      </c>
+      <c r="D25" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="35" customHeight="1">
+      <c r="A26" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>仕訳データ自動作成</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>請求書や取引データから勘定科目を推定し会計仕訳データを自動生成</t>
+        </is>
+      </c>
+      <c r="D26" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="25" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>マーケティング分析</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+    </row>
+    <row r="28" ht="35" customHeight="1">
+      <c r="A28" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>SEO監査・キーワード分析</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>キーワードリサーチ・オンページ分析・コンテンツギャップ・技術チェック・競合比較</t>
+        </is>
+      </c>
+      <c r="D28" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="35" customHeight="1">
+      <c r="A29" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>顧客セグメンテーション分析</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>顧客データベースから行動パターンを特定しセグメント別メッセージング提案まで</t>
+        </is>
+      </c>
+      <c r="D29" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="35" customHeight="1">
+      <c r="A30" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>キャンペーンパフォーマンス分析</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>過去3年分のキャンペーンレポートを分析し成功/失敗パターンと予算ROIの関係性分析</t>
+        </is>
+      </c>
+      <c r="D30" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="35" customHeight="1">
+      <c r="A31" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>SNSトレンド分析</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>Chrome拡張連携で特定キーワードのSNS投稿を収集しトレンド分析</t>
+        </is>
+      </c>
+      <c r="D31" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="35" customHeight="1">
+      <c r="A32" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>メールマーケティング分析</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>A/Bテスト結果・開封率・クリック率データを分析し最適化提案</t>
+        </is>
+      </c>
+      <c r="D32" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="25" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>HRデータ・人事分析</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
+    </row>
+    <row r="34" ht="35" customHeight="1">
+      <c r="A34" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>従業員データ分析→エグゼクティブインサイト</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>9ファイルの人事データをPowerPointで経営層向けインサイトに変換。実測15分</t>
+        </is>
+      </c>
+      <c r="D34" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="35" customHeight="1">
+      <c r="A35" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>離職率分析・予測</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>従業員データから離職パターンを特定しリスク要因と対策提案を含むレポート</t>
+        </is>
+      </c>
+      <c r="D35" s="47" t="inlineStr">
+        <is>
+          <t>論理的導出</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="35" customHeight="1">
+      <c r="A36" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>採用パイプライン分析</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>各ステージ通過率・ソース別効果・コスト分析を自動集計</t>
+        </is>
+      </c>
+      <c r="D36" s="47" t="inlineStr">
+        <is>
+          <t>論理的導出</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="25" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>カスタマーサポート・プロダクト分析</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="17" t="n"/>
+    </row>
+    <row r="38" ht="35" customHeight="1">
+      <c r="A38" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>サポートチケット分類・トリアージ分析</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>受信チケットを構造化カテゴリと優先度で自動分類し傾向分析レポートを生成</t>
+        </is>
+      </c>
+      <c r="D38" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="35" customHeight="1">
+      <c r="A39" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>CSAT/NPS分析</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>顧客満足度・推奨度スコアの推移分析と要因分析</t>
+        </is>
+      </c>
+      <c r="D39" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="35" customHeight="1">
+      <c r="A40" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>ユーザー行動分析</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>PostHog等からDAUデータをダウンロードしトレンド分析スプレッドシートを自動生成</t>
+        </is>
+      </c>
+      <c r="D40" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="35" customHeight="1">
+      <c r="A41" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>VOC（Voice of Customer）分析</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>フィードバック・レビュー・問い合わせデータからテーマ抽出し製品改善提案レポートを生成</t>
+        </is>
+      </c>
+      <c r="D41" s="47" t="inlineStr">
+        <is>
+          <t>論理的導出</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="25" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>学術・科学リサーチ</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="17" t="n"/>
+    </row>
+    <row r="43" ht="35" customHeight="1">
+      <c r="A43" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>論文・文献サーベイ</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>PubMed/bioRxiv/Nature等から文献検索しサマリーを作成</t>
+        </is>
+      </c>
+      <c r="D43" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="35" customHeight="1">
+      <c r="A44" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>ゲノミクス・バイオインフォマティクス分析</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>ChEMBL/Open Targets/Benchling連携でターゲット優先順位付けやゲノム解析を支援</t>
+        </is>
+      </c>
+      <c r="D44" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="35" customHeight="1">
+      <c r="A45" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>臨床試験データ分析</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>ClinicalTrials.gov連携で試験データの検索・分析・要約を自動化</t>
+        </is>
+      </c>
+      <c r="D45" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="35" customHeight="1">
+      <c r="A46" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B46" s="19" t="inlineStr">
+        <is>
+          <t>リサーチ統合・メタ分析</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>複数PDFから共通KPIを特定しメタ分析サマリーノートと比較チャートを自動作成</t>
+        </is>
+      </c>
+      <c r="D46" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="25" customHeight="1">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>医療・ヘルスケアデータ分析</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="n"/>
+      <c r="C47" s="17" t="n"/>
+      <c r="D47" s="17" t="n"/>
+    </row>
+    <row r="48" ht="35" customHeight="1">
+      <c r="A48" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>電子カルテ（EHR）データ要約</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t>過去の来院記録・薬の変更・検査数値の推移を数秒で要約</t>
+        </is>
+      </c>
+      <c r="D48" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="35" customHeight="1">
+      <c r="A49" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>健康データ統合分析</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>Apple Health/Android Health Connect連携で分散した健康データを統合分析</t>
+        </is>
+      </c>
+      <c r="D49" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="35" customHeight="1">
+      <c r="A50" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B50" s="19" t="inlineStr">
+        <is>
+          <t>医療コーディング・分類支援</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="inlineStr">
+        <is>
+          <t>ICD-10データベースと連携し疾病分類や医療コーディングを支援</t>
+        </is>
+      </c>
+      <c r="D50" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="25" customHeight="1">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>エンタープライズ情報検索・統合</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="n"/>
+      <c r="C51" s="17" t="n"/>
+      <c r="D51" s="17" t="n"/>
+    </row>
+    <row r="52" ht="35" customHeight="1">
+      <c r="A52" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B52" s="19" t="inlineStr">
+        <is>
+          <t>社内ナレッジ横断検索</t>
+        </is>
+      </c>
+      <c r="C52" s="20" t="inlineStr">
+        <is>
+          <t>Slack/Google Drive/Jira等の社内ツール横断でセマンティック検索</t>
+        </is>
+      </c>
+      <c r="D52" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="35" customHeight="1">
+      <c r="A53" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t>社内ドキュメント統合レポート作成</t>
+        </is>
+      </c>
+      <c r="C53" s="20" t="inlineStr">
+        <is>
+          <t>複数社内資料・議事録・メモを横断読み込みサマリーレポートを生成</t>
+        </is>
+      </c>
+      <c r="D53" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="35" customHeight="1">
+      <c r="A54" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B54" s="19" t="inlineStr">
+        <is>
+          <t>会議録・インタビュー分析</t>
+        </is>
+      </c>
+      <c r="C54" s="20" t="inlineStr">
+        <is>
+          <t>トランスクリプトからテーマ・キーポイント・アクションアイテムを自動抽出</t>
+        </is>
+      </c>
+      <c r="D54" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="25" customHeight="1">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>CSVレポート・定型業務</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="n"/>
+      <c r="C55" s="17" t="n"/>
+      <c r="D55" s="17" t="n"/>
+    </row>
+    <row r="56" ht="35" customHeight="1">
+      <c r="A56" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B56" s="19" t="inlineStr">
+        <is>
+          <t>CSV→Excelレポート自動変換</t>
+        </is>
+      </c>
+      <c r="C56" s="20" t="inlineStr">
+        <is>
+          <t>CSVをドロップするだけでサマリー・グラフ・インサイトを含むExcelレポートを数十秒で生成</t>
+        </is>
+      </c>
+      <c r="D56" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="35" customHeight="1">
+      <c r="A57" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B57" s="19" t="inlineStr">
+        <is>
+          <t>定型レポートの週次バッチ処理</t>
+        </is>
+      </c>
+      <c r="C57" s="20" t="inlineStr">
+        <is>
+          <t>毎週のCSVに同一フォーマット処理（重複削除・ソート・合計追加）を自動適用</t>
+        </is>
+      </c>
+      <c r="D57" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="35" customHeight="1">
+      <c r="A58" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B58" s="19" t="inlineStr">
+        <is>
+          <t>複数PDF比較分析</t>
+        </is>
+      </c>
+      <c r="C58" s="20" t="inlineStr">
+        <is>
+          <t>複数PDFレポートを読み込み部門間パフォーマンス比較チャートを自動作成</t>
+        </is>
+      </c>
+      <c r="D58" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="35" customHeight="1">
+      <c r="A59" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B59" s="19" t="inlineStr">
+        <is>
+          <t>在庫管理・リオーダーアラート分析</t>
+        </is>
+      </c>
+      <c r="C59" s="20" t="inlineStr">
+        <is>
+          <t>在庫データから適正水準を計算しリオーダーアラートと在庫評価レポートを生成</t>
+        </is>
+      </c>
+      <c r="D59" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="25" customHeight="1">
+      <c r="A60" s="16" t="inlineStr">
+        <is>
+          <t>法務・コンプライアンス分析</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="n"/>
+      <c r="C60" s="17" t="n"/>
+      <c r="D60" s="17" t="n"/>
+    </row>
+    <row r="61" ht="35" customHeight="1">
+      <c r="A61" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B61" s="19" t="inlineStr">
+        <is>
+          <t>契約書リスク分析</t>
+        </is>
+      </c>
+      <c r="C61" s="20" t="inlineStr">
+        <is>
+          <t>契約書を条項ごとに分析し法的リスク箇所の特定・Redline・修正理由を自動生成</t>
+        </is>
+      </c>
+      <c r="D61" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="35" customHeight="1">
+      <c r="A62" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B62" s="19" t="inlineStr">
+        <is>
+          <t>規制コンプライアンス追跡</t>
+        </is>
+      </c>
+      <c r="C62" s="20" t="inlineStr">
+        <is>
+          <t>規制変更を追跡し自社への影響を分析してコンプライアンスレポートを作成</t>
+        </is>
+      </c>
+      <c r="D62" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="25" customHeight="1">
+      <c r="A63" s="16" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="n"/>
+      <c r="C63" s="17" t="n"/>
+      <c r="D63" s="17" t="n"/>
+    </row>
+    <row r="64" ht="35" customHeight="1">
+      <c r="A64" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B64" s="19" t="inlineStr">
+        <is>
+          <t>ログデータの異常値スクリーニング</t>
+        </is>
+      </c>
+      <c r="C64" s="20" t="inlineStr">
+        <is>
+          <t>CSVやログファイルで条件指定の異常検知一次スクリーニングを実行</t>
+        </is>
+      </c>
+      <c r="D64" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="35" customHeight="1">
+      <c r="A65" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B65" s="19" t="inlineStr">
+        <is>
+          <t>パーソナルナレッジ統合分析</t>
+        </is>
+      </c>
+      <c r="C65" s="20" t="inlineStr">
+        <is>
+          <t>個人のメモ・日記・リサーチファイルを分析しパターン・テーマ・接続点を発見</t>
+        </is>
+      </c>
+      <c r="D65" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="A63:D63"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5653,17 +7903,1081 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>6.顧客・人事・教育系（Markdownファイル docs/cowork-usecases.md を参照）</t>
+    <row r="1" ht="35" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>6. 顧客対応・人事・教育系（50件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>活用用途</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>信頼度</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>カスタマーサポート</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+    </row>
+    <row r="5" ht="35" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>チケットトリアージ（分類・優先度判定）</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>/triageコマンドで受信チケットをカテゴリ・緊急度・ルーティング先に自動分類</t>
+        </is>
+      </c>
+      <c r="D5" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="35" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>問い合わせ回答ドラフト作成</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>/draft-responseで状況・緊急度・チャネルに応じた返信文を自動生成</t>
+        </is>
+      </c>
+      <c r="D6" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="35" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>エスカレーション資料の自動作成</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>/escalateで再現手順・ビジネスインパクト・コンテキストをパッケージ化</t>
+        </is>
+      </c>
+      <c r="D7" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="35" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>ナレッジベース記事の自動生成</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>/kb-articleで解決済みチケットからセルフサービス用KB記事を作成</t>
+        </is>
+      </c>
+      <c r="D8" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="35" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>複数ソースからの顧客調査</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>/researchでチケット・メール・Slackを横断検索しテーマ特定・引用付き回答を合成</t>
+        </is>
+      </c>
+      <c r="D9" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="35" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>FAQ文書の自動作成</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>サポートメールを読み込ませ最も多い質問とその回答をFAQドキュメントとして生成</t>
+        </is>
+      </c>
+      <c r="D10" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="35" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>顧客フィードバックの感情分析・テーマ抽出</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>コールトランスクリプト・CRMノートからパターンを特定し改善案を優先度付きで提示</t>
+        </is>
+      </c>
+      <c r="D11" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="35" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>多言語カスタマーサポート対応</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>200以上の言語で対話可能。言語ごとの別チャットボットや翻訳プロセスが不要</t>
+        </is>
+      </c>
+      <c r="D12" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="35" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>顧客対応メールテンプレートの一括作成</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>共通問い合わせパターンに対しパーソナライズ余地を残したテンプレートセットを生成</t>
+        </is>
+      </c>
+      <c r="D13" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="35" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>クレーム対応レスポンスの作成</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>苦情内容を分析し適切なトーンと解決策を含む返信ドラフトを自動作成</t>
+        </is>
+      </c>
+      <c r="D14" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="35" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>朝のメールトリアージ自動化</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>メール優先度分類・カテゴリ分け・返信ドラフト作成をダッシュボード形式で出力</t>
+        </is>
+      </c>
+      <c r="D15" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="35" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>顧客オンボーディングパッケージの作成</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>メール・メモ・テンプレートから新規顧客向けウェルカムキットを統合文書として作成</t>
+        </is>
+      </c>
+      <c r="D16" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="35" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>クライアントミーティング用Flash Brief作成</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>顧客ファイルからプロジェクト状況・未払い請求・アップセル機会をサマリー化</t>
+        </is>
+      </c>
+      <c r="D17" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="35" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>サポート品質レポートの自動生成</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>チケットデータから対応時間・解決率・顧客満足度などのKPIレポートを出力</t>
+        </is>
+      </c>
+      <c r="D18" s="47" t="inlineStr">
+        <is>
+          <t>論理的導出</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="35" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>VoC（顧客の声）レポート作成</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>複数チャネルからの顧客フィードバックを集約・分析し経営層向けレポートにまとめる</t>
+        </is>
+      </c>
+      <c r="D19" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="35" customHeight="1">
+      <c r="A20" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>サポート対応マニュアル（SOP）の作成</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>散在するドキュメントから新人サポートスタッフ向け手順書を自動作成</t>
+        </is>
+      </c>
+      <c r="D20" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="35" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>チャットボット応答スクリプトの作成</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>過去ログからチャットボット用の応答スクリプト・フローを設計・文書化</t>
+        </is>
+      </c>
+      <c r="D21" s="47" t="inlineStr">
+        <is>
+          <t>論理的導出</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="35" customHeight="1">
+      <c r="A22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>返金・キャンセルポリシーの文書整備</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>散在するポリシー文書を統合し一貫性のある顧客向けポリシー文書を作成</t>
+        </is>
+      </c>
+      <c r="D22" s="47" t="inlineStr">
+        <is>
+          <t>論理的導出</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="35" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>顧客セグメント別対応ガイドの作成</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>CRMデータやチケット履歴から顧客セグメントごとの対応方針をまとめたガイド作成</t>
+        </is>
+      </c>
+      <c r="D23" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="35" customHeight="1">
+      <c r="A24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>サポートチーム週次/月次サマリーレポート</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>チケット傾向・対応件数・頻出問題をExcel/PowerPointで自動レポート化</t>
+        </is>
+      </c>
+      <c r="D24" s="47" t="inlineStr">
+        <is>
+          <t>論理的導出</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="25" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>人事（HR）</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+    </row>
+    <row r="26" ht="35" customHeight="1">
+      <c r="A26" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>求人票（Job Description）の作成</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>ポジション要件からスキル・責任範囲・応募条件を含む求人票を自動生成</t>
+        </is>
+      </c>
+      <c r="D26" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="35" customHeight="1">
+      <c r="A27" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>履歴書/CVスクリーニング</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>求人要件と照合して候補者適合度を評価し最も合致する候補者をハイライト</t>
+        </is>
+      </c>
+      <c r="D27" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="35" customHeight="1">
+      <c r="A28" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>面接質問の生成</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>候補者のスキル・経験に合わせたカスタマイズ面接質問を自動作成</t>
+        </is>
+      </c>
+      <c r="D28" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="35" customHeight="1">
+      <c r="A29" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>候補者コミュニケーションメール下書き</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>選考結果通知・面接日程調整・オファーレターの候補者向けメールを自動ドラフト</t>
+        </is>
+      </c>
+      <c r="D29" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="35" customHeight="1">
+      <c r="A30" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>HRデータ分析→経営層向けレポート</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>9ファイルの人事データをPowerPointで経営層向けインサイトに変換。15分で完了</t>
+        </is>
+      </c>
+      <c r="D30" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="35" customHeight="1">
+      <c r="A31" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>新入社員オンボーディングガイドの作成</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>会社文化・初期トレーニング・メンター割り当て・必要リソースを含むガイドを設計</t>
+        </is>
+      </c>
+      <c r="D31" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="35" customHeight="1">
+      <c r="A32" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>パフォーマンスレビュー指標の設計</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>ポジションごとに組織目標に整合したパフォーマンス指標を提案</t>
+        </is>
+      </c>
+      <c r="D32" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="35" customHeight="1">
+      <c r="A33" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>面接トランスクリプトの文字起こし・要約</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>面接録音の文字起こしと要約を行い候補者評価情報を構造化抽出</t>
+        </is>
+      </c>
+      <c r="D33" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="35" customHeight="1">
+      <c r="A34" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>採用データ分析</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>採用パイプラインのボトルネック・歩留まり・チャネル効果を可視化</t>
+        </is>
+      </c>
+      <c r="D34" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="35" customHeight="1">
+      <c r="A35" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>従業員エンゲージメント調査の分析</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>アンケート結果からテーマ抽出・改善提案・経営層向けサマリーを作成</t>
+        </is>
+      </c>
+      <c r="D35" s="47" t="inlineStr">
+        <is>
+          <t>論理的導出</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="35" customHeight="1">
+      <c r="A36" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>社内規程・就業規則の文書整備</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>散在する社内規程を統合・整理し一貫性のある規程文書を作成</t>
+        </is>
+      </c>
+      <c r="D36" s="47" t="inlineStr">
+        <is>
+          <t>論理的導出</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="35" customHeight="1">
+      <c r="A37" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>退職面談（Exit Interview）の分析</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>退職面談記録から退職理由パターン・改善領域をレポート化</t>
+        </is>
+      </c>
+      <c r="D37" s="47" t="inlineStr">
+        <is>
+          <t>論理的導出</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="35" customHeight="1">
+      <c r="A38" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>給与・報酬ベンチマークレポート</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>社内給与データと市場データを比較分析し報酬の競争力レポートを作成</t>
+        </is>
+      </c>
+      <c r="D38" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="35" customHeight="1">
+      <c r="A39" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>組織図・チーム構成の文書化</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>人事データからチーム構成・レポートライン・役割分担を文書として生成</t>
+        </is>
+      </c>
+      <c r="D39" s="47" t="inlineStr">
+        <is>
+          <t>論理的導出</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="35" customHeight="1">
+      <c r="A40" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>コンプライアンス研修記録の管理</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>研修受講状況を追跡し未受講者リスト・期限切れ資格のアラートレポートを作成</t>
+        </is>
+      </c>
+      <c r="D40" s="47" t="inlineStr">
+        <is>
+          <t>論理的導出</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="35" customHeight="1">
+      <c r="A41" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>人員計画（Workforce Planning）資料の作成</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>人員配置・将来の採用ニーズ・スキルギャップを分析したプランニング文書を作成</t>
+        </is>
+      </c>
+      <c r="D41" s="47" t="inlineStr">
+        <is>
+          <t>論理的導出</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="35" customHeight="1">
+      <c r="A42" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>パートナーメール一括作成</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>採用パートナー・人材紹介会社への連絡メールを大量に自動ドラフト（47通作成の実績あり）</t>
+        </is>
+      </c>
+      <c r="D42" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="25" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>教育・研修・ナレッジ管理</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+    </row>
+    <row r="44" ht="35" customHeight="1">
+      <c r="A44" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>SOP（標準作業手順書）の自動作成</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>散在するドキュメントを分析し新入社員向けステップバイステップ手順書を生成</t>
+        </is>
+      </c>
+      <c r="D44" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="35" customHeight="1">
+      <c r="A45" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>研修資料（PowerPoint/スライド）の作成</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>テキスト・PDFを読み込みPowerPoint形式の研修スライドをスピーカーノート付きで生成</t>
+        </is>
+      </c>
+      <c r="D45" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="35" customHeight="1">
+      <c r="A46" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B46" s="19" t="inlineStr">
+        <is>
+          <t>社内ナレッジの統合・構造化</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>散在するメモ・メール・ドキュメントからテーマ別社内ナレッジベースを構築</t>
+        </is>
+      </c>
+      <c r="D46" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="35" customHeight="1">
+      <c r="A47" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>会議議事録の自動作成</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t>文字起こしから要約・決定事項・アクションアイテム・次回タスクを構造化（15万字まで）</t>
+        </is>
+      </c>
+      <c r="D47" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="35" customHeight="1">
+      <c r="A48" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>eラーニングコンテンツの原稿作成</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t>業務知識を体系的に整理しeラーニング用教材テキスト・クイズ・確認問題を生成</t>
+        </is>
+      </c>
+      <c r="D48" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="35" customHeight="1">
+      <c r="A49" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>業務マニュアルのバージョン更新</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>既存マニュアルの改定必要箇所を特定し最新情報を反映した更新版を作成</t>
+        </is>
+      </c>
+      <c r="D49" s="47" t="inlineStr">
+        <is>
+          <t>論理的導出</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="35" customHeight="1">
+      <c r="A50" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B50" s="19" t="inlineStr">
+        <is>
+          <t>インタビュー記録からのインサイト抽出</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="inlineStr">
+        <is>
+          <t>インタビュー録やアンケートからテーマ・キーポイントを自動抽出し構造化レポートとして出力</t>
+        </is>
+      </c>
+      <c r="D50" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="35" customHeight="1">
+      <c r="A51" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B51" s="19" t="inlineStr">
+        <is>
+          <t>AI活用研修の導入計画策定</t>
+        </is>
+      </c>
+      <c r="C51" s="20" t="inlineStr">
+        <is>
+          <t>組織全体のAI活用推進に向けた導入計画・教育プログラム・ROI測定フレームワークを設計</t>
+        </is>
+      </c>
+      <c r="D51" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="35" customHeight="1">
+      <c r="A52" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B52" s="19" t="inlineStr">
+        <is>
+          <t>製品/サービスの内部トレーニング資料作成</t>
+        </is>
+      </c>
+      <c r="C52" s="20" t="inlineStr">
+        <is>
+          <t>製品ドキュメント・リリースノートから営業/CS向け製品知識トレーニング資料を生成</t>
+        </is>
+      </c>
+      <c r="D52" s="47" t="inlineStr">
+        <is>
+          <t>論理的導出</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="35" customHeight="1">
+      <c r="A53" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t>プロダクト仕様書（PRD）の自動生成</t>
+        </is>
+      </c>
+      <c r="C53" s="20" t="inlineStr">
+        <is>
+          <t>/write-specで問題定義からユーザーストーリー・要件優先度・成功指標を含むPRDを生成</t>
+        </is>
+      </c>
+      <c r="D53" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="35" customHeight="1">
+      <c r="A54" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B54" s="19" t="inlineStr">
+        <is>
+          <t>顧客ユーザーリサーチの統合分析</t>
+        </is>
+      </c>
+      <c r="C54" s="20" t="inlineStr">
+        <is>
+          <t>/synthesize-researchでインタビューノートとアンケートを構造化インサイトに変換</t>
+        </is>
+      </c>
+      <c r="D54" s="48" t="inlineStr">
+        <is>
+          <t>公式プラグイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="35" customHeight="1">
+      <c r="A55" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B55" s="19" t="inlineStr">
+        <is>
+          <t>補助金申請書・事業計画書の下書き作成</t>
+        </is>
+      </c>
+      <c r="C55" s="20" t="inlineStr">
+        <is>
+          <t>必要情報を整理しフォーマットに沿った補助金申請書や事業計画書のドラフトを自動作成</t>
+        </is>
+      </c>
+      <c r="D55" s="46" t="inlineStr">
+        <is>
+          <t>記事確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="35" customHeight="1">
+      <c r="A56" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B56" s="19" t="inlineStr">
+        <is>
+          <t>社内コミュニケーション文書（全社メモ・通達）の作成</t>
+        </is>
+      </c>
+      <c r="C56" s="20" t="inlineStr">
+        <is>
+          <t>ポリシー変更・組織変更等の全社通達文書を適切なトーンとフォーマットで自動生成</t>
+        </is>
+      </c>
+      <c r="D56" s="47" t="inlineStr">
+        <is>
+          <t>論理的導出</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A25:D25"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>